--- a/output/roomself_excel/1858.xlsx
+++ b/output/roomself_excel/1858.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>143178</v>
+        <v>67151</v>
       </c>
       <c r="D2" t="n">
-        <v>3700</v>
+        <v>2092</v>
       </c>
       <c r="E2" t="n">
-        <v>1124</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>56160</v>
+        <v>202088</v>
       </c>
       <c r="D3" t="n">
-        <v>2044</v>
+        <v>4080</v>
       </c>
       <c r="E3" t="n">
-        <v>946</v>
+        <v>392</v>
       </c>
       <c r="F3" t="n">
-        <v>373</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15589</v>
+        <v>119270</v>
       </c>
       <c r="D4" t="n">
-        <v>1000</v>
+        <v>2780</v>
       </c>
       <c r="E4" t="n">
-        <v>131</v>
+        <v>450</v>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
+        <v>333</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,86 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>307810</v>
+        <v>56160</v>
       </c>
       <c r="D5" t="n">
-        <v>5384</v>
+        <v>2044</v>
       </c>
       <c r="E5" t="n">
-        <v>946</v>
+        <v>373</v>
       </c>
       <c r="F5" t="n">
-        <v>559</v>
+        <v>181</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Hallway</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>38571</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1752</v>
+      </c>
+      <c r="E6" t="n">
+        <v>174</v>
+      </c>
+      <c r="F6" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>23908</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1264</v>
+      </c>
+      <c r="E7" t="n">
+        <v>161</v>
+      </c>
+      <c r="F7" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>15589</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E8" t="n">
+        <v>131</v>
+      </c>
+      <c r="F8" t="n">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/1858.xlsx
+++ b/output/roomself_excel/1858.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,62 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
         </is>
       </c>
     </row>
@@ -475,12 +525,18 @@
       <c r="D2" t="n">
         <v>2092</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +553,34 @@
       <c r="D3" t="n">
         <v>4080</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>392</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>34</v>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>628</v>
+      </c>
+      <c r="J3" t="n">
+        <v>20</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,11 +597,49 @@
       <c r="D4" t="n">
         <v>2780</v>
       </c>
-      <c r="E4" t="n">
-        <v>450</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>333</v>
+        <v>382</v>
+      </c>
+      <c r="G4" t="n">
+        <v>21</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>156</v>
+      </c>
+      <c r="J4" t="n">
+        <v>22</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>84</v>
+      </c>
+      <c r="M4" t="n">
+        <v>46</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>193</v>
+      </c>
+      <c r="P4" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="5">
@@ -541,12 +657,34 @@
       <c r="D5" t="n">
         <v>2044</v>
       </c>
-      <c r="E5" t="n">
-        <v>373</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>181</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="G5" t="n">
+        <v>22</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>351</v>
+      </c>
+      <c r="J5" t="n">
+        <v>21</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +701,42 @@
       <c r="D6" t="n">
         <v>1752</v>
       </c>
-      <c r="E6" t="n">
-        <v>174</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>56</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="G6" t="n">
+        <v>21</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>79</v>
+      </c>
+      <c r="J6" t="n">
+        <v>36</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>184</v>
+      </c>
+      <c r="M6" t="n">
+        <v>20</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +753,26 @@
       <c r="D7" t="n">
         <v>1264</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>161</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>22</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +789,26 @@
       <c r="D8" t="n">
         <v>1000</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>131</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>32</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/1858.xlsx
+++ b/output/roomself_excel/1858.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:X8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +507,46 @@
       <c r="P1" s="1" t="inlineStr">
         <is>
           <t>ExtWallWidth_4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
         </is>
       </c>
     </row>
@@ -537,6 +577,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -581,6 +629,38 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>184</v>
+      </c>
+      <c r="T3" t="n">
+        <v>34</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>84</v>
+      </c>
+      <c r="X3" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -641,6 +721,26 @@
       <c r="P4" t="n">
         <v>34</v>
       </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>163</v>
+      </c>
+      <c r="T4" t="n">
+        <v>34</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -685,6 +785,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -737,6 +845,26 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>95</v>
+      </c>
+      <c r="T6" t="n">
+        <v>20</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -773,6 +901,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -809,6 +945,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
